--- a/table/resources/sample/AirRaid.xlsx
+++ b/table/resources/sample/AirRaid.xlsx
@@ -70,6 +70,28 @@
         </r>
       </text>
     </comment>
+    <comment ref="G1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+在此值上除以10000</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="H1" authorId="1">
       <text>
         <r>
@@ -88,7 +110,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-每0.1秒增长(在此值上除以100)</t>
+坠毁概率的增加值
+在此值上除以10000</t>
         </r>
       </text>
     </comment>
@@ -110,7 +133,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-每次增长时判断是否坠毁（在此值上除以100）</t>
+在此值上除以10000
+</t>
         </r>
       </text>
     </comment>
@@ -202,7 +226,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="38">
   <si>
     <t xml:space="preserve">id </t>
   </si>
@@ -222,13 +246,13 @@
     <t>单线押分值</t>
   </si>
   <si>
-    <t>秒</t>
-  </si>
-  <si>
-    <t>增长倍数</t>
-  </si>
-  <si>
-    <t>坠毁概率</t>
+    <t>倍数增长率（r）</t>
+  </si>
+  <si>
+    <t>风险增量（k）</t>
+  </si>
+  <si>
+    <t>初始坠毁率（p0）</t>
   </si>
   <si>
     <t>玩家赢抽水</t>
@@ -276,10 +300,13 @@
     <t>betList</t>
   </si>
   <si>
-    <t>Growthmultiplier</t>
-  </si>
-  <si>
-    <t>Crashduration</t>
+    <t>GrowthMultiplier</t>
+  </si>
+  <si>
+    <t>RiskIncrement</t>
+  </si>
+  <si>
+    <t>InitialCrashRate</t>
   </si>
   <si>
     <t>WinRatio</t>
@@ -974,7 +1001,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1016,9 +1043,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1042,7 +1066,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1576,23 +1600,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="7.375" style="3" customWidth="1"/>
     <col min="3" max="3" width="12.875" style="3" customWidth="1"/>
     <col min="4" max="4" width="22.5" style="3" customWidth="1"/>
     <col min="5" max="5" width="24.375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="13.75" style="3" customWidth="1"/>
-    <col min="7" max="7" width="4.875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12.5" style="3" customWidth="1"/>
+    <col min="6" max="6" width="17.125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="17.5" style="3" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="3" customWidth="1"/>
     <col min="9" max="9" width="15" style="4" customWidth="1"/>
     <col min="10" max="10" width="11.125" style="3" customWidth="1"/>
     <col min="11" max="11" width="10.125" style="3" customWidth="1"/>
     <col min="12" max="12" width="14.5" style="3" customWidth="1"/>
     <col min="13" max="13" width="15.125" style="3" customWidth="1"/>
     <col min="14" max="14" width="16.25" style="3" customWidth="1"/>
-    <col min="15" max="17" width="9" style="3"/>
+    <col min="15" max="15" width="21.875" style="3" customWidth="1"/>
+    <col min="16" max="16" width="20.375" style="3" customWidth="1"/>
+    <col min="17" max="17" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="16.5" spans="1:17">
@@ -1638,8 +1664,8 @@
       <c r="N1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
+      <c r="O1"/>
+      <c r="P1"/>
       <c r="Q1" s="5"/>
     </row>
     <row r="2" s="2" customFormat="1" ht="16.5" spans="1:17">
@@ -1659,11 +1685,13 @@
       <c r="F2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="12"/>
+      <c r="G2" s="13" t="s">
+        <v>14</v>
+      </c>
       <c r="H2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="10" t="s">
         <v>14</v>
       </c>
       <c r="J2" s="8" t="s">
@@ -1672,17 +1700,17 @@
       <c r="K2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="L2" s="14" t="s">
         <v>15</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="16" t="s">
+      <c r="N2" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
+      <c r="O2"/>
+      <c r="P2"/>
       <c r="Q2" s="12"/>
     </row>
     <row r="3" s="2" customFormat="1" ht="16.5" spans="1:17">
@@ -1702,30 +1730,32 @@
       <c r="F3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="12"/>
+      <c r="G3" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="H3" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="I3" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="18" t="s">
+      <c r="J3" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="19" t="s">
+      <c r="K3" s="17" t="s">
         <v>28</v>
       </c>
+      <c r="L3" s="18" t="s">
+        <v>29</v>
+      </c>
       <c r="M3" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="O3" s="12"/>
-      <c r="P3" s="12"/>
+      <c r="N3" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3"/>
+      <c r="P3"/>
       <c r="Q3" s="12"/>
     </row>
     <row r="4" s="2" customFormat="1" ht="16.5" spans="1:17">
@@ -1737,14 +1767,14 @@
       <c r="F4" s="12"/>
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
-      <c r="I4" s="21"/>
+      <c r="I4" s="20"/>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
       <c r="L4" s="9"/>
       <c r="M4" s="10"/>
       <c r="N4" s="11"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="12"/>
+      <c r="O4"/>
+      <c r="P4"/>
       <c r="Q4" s="12"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:17">
@@ -1755,25 +1785,25 @@
         <v>400400</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" s="5">
         <v>40040001</v>
       </c>
-      <c r="E5" s="22" t="s">
-        <v>32</v>
+      <c r="E5" s="21" t="s">
+        <v>33</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G5" s="5">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="H5" s="5">
-        <v>10</v>
-      </c>
-      <c r="I5" s="23">
-        <v>50</v>
+        <v>60</v>
+      </c>
+      <c r="I5" s="22">
+        <v>300</v>
       </c>
       <c r="J5" s="8">
         <v>300</v>
@@ -1781,555 +1811,132 @@
       <c r="K5" s="8">
         <v>10000</v>
       </c>
-      <c r="L5" s="25" t="s">
-        <v>34</v>
+      <c r="L5" s="24" t="s">
+        <v>35</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="N5" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
+      <c r="N5" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="O5"/>
+      <c r="P5"/>
       <c r="Q5" s="5"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A6" s="1">
-        <v>400402</v>
-      </c>
-      <c r="B6" s="5">
-        <v>400400</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="5">
-        <v>40040001</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" s="5">
-        <v>2</v>
-      </c>
-      <c r="H6" s="5">
-        <v>15</v>
-      </c>
-      <c r="I6" s="23">
-        <v>50</v>
-      </c>
-      <c r="J6" s="8">
-        <v>300</v>
-      </c>
-      <c r="K6" s="8">
-        <v>10000</v>
-      </c>
-      <c r="L6" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M6" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="N6" s="24" t="s">
-        <v>36</v>
-      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A7" s="1">
-        <v>400403</v>
-      </c>
-      <c r="B7" s="5">
-        <v>400400</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="5">
-        <v>40040001</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="5">
-        <v>3</v>
-      </c>
-      <c r="H7" s="5">
-        <v>20</v>
-      </c>
-      <c r="I7" s="23">
-        <v>65</v>
-      </c>
-      <c r="J7" s="8">
-        <v>300</v>
-      </c>
-      <c r="K7" s="8">
-        <v>10000</v>
-      </c>
-      <c r="L7" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M7" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="N7" s="24" t="s">
-        <v>36</v>
-      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
       <c r="O7" s="5"/>
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A8" s="1">
-        <v>400404</v>
-      </c>
-      <c r="B8" s="5">
-        <v>400400</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="5">
-        <v>40040001</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="5">
-        <v>4</v>
-      </c>
-      <c r="H8" s="5">
-        <v>25</v>
-      </c>
-      <c r="I8" s="23">
-        <v>65</v>
-      </c>
-      <c r="J8" s="8">
-        <v>300</v>
-      </c>
-      <c r="K8" s="8">
-        <v>10000</v>
-      </c>
-      <c r="L8" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M8" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="N8" s="24" t="s">
-        <v>36</v>
-      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
     </row>
-    <row r="9" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A9" s="1">
-        <v>400405</v>
-      </c>
-      <c r="B9" s="5">
-        <v>400400</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="5">
-        <v>40040001</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="5">
-        <v>5</v>
-      </c>
-      <c r="H9" s="5">
-        <v>30</v>
-      </c>
-      <c r="I9" s="23">
-        <v>70</v>
-      </c>
-      <c r="J9" s="8">
-        <v>300</v>
-      </c>
-      <c r="K9" s="8">
-        <v>10000</v>
-      </c>
-      <c r="L9" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M9" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="N9" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A10" s="1">
-        <v>400406</v>
-      </c>
-      <c r="B10" s="5">
-        <v>400400</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="5">
-        <v>40040001</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="5">
-        <v>6</v>
-      </c>
-      <c r="H10" s="5">
-        <v>35</v>
-      </c>
-      <c r="I10" s="23">
-        <v>70</v>
-      </c>
-      <c r="J10" s="8">
-        <v>300</v>
-      </c>
-      <c r="K10" s="8">
-        <v>10000</v>
-      </c>
-      <c r="L10" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M10" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="N10" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A11" s="1">
-        <v>400407</v>
-      </c>
-      <c r="B11" s="5">
-        <v>400400</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="5">
-        <v>40040001</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" s="5">
-        <v>7</v>
-      </c>
-      <c r="H11" s="5">
-        <v>40</v>
-      </c>
-      <c r="I11" s="23">
-        <v>75</v>
-      </c>
-      <c r="J11" s="8">
-        <v>300</v>
-      </c>
-      <c r="K11" s="8">
-        <v>10000</v>
-      </c>
-      <c r="L11" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M11" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="N11" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A12" s="1">
-        <v>400408</v>
-      </c>
-      <c r="B12" s="5">
-        <v>400400</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="5">
-        <v>40040001</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="5">
-        <v>8</v>
-      </c>
-      <c r="H12" s="5">
-        <v>45</v>
-      </c>
-      <c r="I12" s="23">
-        <v>75</v>
-      </c>
-      <c r="J12" s="8">
-        <v>300</v>
-      </c>
-      <c r="K12" s="8">
-        <v>10000</v>
-      </c>
-      <c r="L12" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M12" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="N12" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A13" s="1">
-        <v>400409</v>
-      </c>
-      <c r="B13" s="5">
-        <v>400400</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="5">
-        <v>40040001</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" s="5">
-        <v>9</v>
-      </c>
-      <c r="H13" s="5">
-        <v>50</v>
-      </c>
-      <c r="I13" s="23">
-        <v>90</v>
-      </c>
-      <c r="J13" s="8">
-        <v>300</v>
-      </c>
-      <c r="K13" s="8">
-        <v>10000</v>
-      </c>
-      <c r="L13" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M13" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="N13" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A14" s="1">
-        <v>400410</v>
-      </c>
-      <c r="B14" s="5">
-        <v>400400</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="5">
-        <v>40040001</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="5">
-        <v>10</v>
-      </c>
-      <c r="H14" s="5">
-        <v>55</v>
-      </c>
-      <c r="I14" s="23">
-        <v>100</v>
-      </c>
-      <c r="J14" s="8">
-        <v>300</v>
-      </c>
-      <c r="K14" s="8">
-        <v>10000</v>
-      </c>
-      <c r="L14" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M14" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="N14" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
+    <row r="9" ht="16.5" spans="1:17">
+      <c r="G9" s="5"/>
+    </row>
+    <row r="10" ht="16.5" spans="1:17">
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" ht="16.5" spans="1:17">
+      <c r="G11" s="5"/>
+    </row>
+    <row r="12" ht="16.5" spans="1:17">
+      <c r="G12" s="5"/>
+    </row>
+    <row r="13" ht="16.5" spans="1:17">
+      <c r="G13" s="5"/>
+    </row>
+    <row r="14" ht="16.5" spans="1:17">
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" ht="16.5" spans="1:17">
       <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
+    </row>
+    <row r="16" ht="16.5" spans="1:17">
       <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="16.5" spans="2:17">
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
+    </row>
+    <row r="17" ht="16.5" spans="7:7">
       <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-    </row>
-    <row r="18" ht="16.5" spans="2:17">
+    </row>
+    <row r="18" ht="16.5" spans="7:7">
       <c r="G18" s="5"/>
     </row>
-    <row r="19" ht="16.5" spans="2:17">
+    <row r="19" ht="16.5" spans="7:7">
       <c r="G19" s="5"/>
     </row>
-    <row r="20" ht="16.5" spans="2:17">
+    <row r="20" ht="16.5" spans="7:7">
       <c r="G20" s="5"/>
     </row>
-    <row r="21" ht="16.5" spans="2:17">
+    <row r="21" ht="16.5" spans="7:7">
       <c r="G21" s="5"/>
     </row>
-    <row r="22" ht="16.5" spans="2:17">
+    <row r="22" ht="16.5" spans="7:7">
       <c r="G22" s="5"/>
     </row>
-    <row r="23" ht="16.5" spans="2:17">
+    <row r="23" ht="16.5" spans="7:7">
       <c r="G23" s="5"/>
     </row>
-    <row r="24" ht="16.5" spans="2:17">
+    <row r="24" ht="16.5" spans="7:7">
       <c r="G24" s="5"/>
     </row>
-    <row r="25" ht="16.5" spans="2:17">
+    <row r="25" ht="16.5" spans="7:7">
       <c r="G25" s="5"/>
     </row>
-    <row r="26" ht="16.5" spans="2:17">
+    <row r="26" ht="16.5" spans="7:7">
       <c r="G26" s="5"/>
     </row>
-    <row r="27" ht="16.5" spans="2:17">
+    <row r="27" ht="16.5" spans="7:7">
       <c r="G27" s="5"/>
     </row>
-    <row r="28" ht="16.5" spans="2:17">
+    <row r="28" ht="16.5" spans="7:7">
       <c r="G28" s="5"/>
-    </row>
-    <row r="29" ht="16.5" spans="2:17">
-      <c r="G29" s="5"/>
-    </row>
-    <row r="30" ht="16.5" spans="2:17">
-      <c r="G30" s="5"/>
-    </row>
-    <row r="31" ht="16.5" spans="2:17">
-      <c r="G31" s="5"/>
-    </row>
-    <row r="32" ht="16.5" spans="2:17">
-      <c r="G32" s="5"/>
-    </row>
-    <row r="33" ht="16.5" spans="7:7">
-      <c r="G33" s="5"/>
-    </row>
-    <row r="34" ht="16.5" spans="7:7">
-      <c r="G34" s="5"/>
-    </row>
-    <row r="35" ht="16.5" spans="7:7">
-      <c r="G35" s="5"/>
-    </row>
-    <row r="36" ht="16.5" spans="7:7">
-      <c r="G36" s="5"/>
-    </row>
-    <row r="37" ht="16.5" spans="7:7">
-      <c r="G37" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
